--- a/ejec_ing_Dep.xlsx
+++ b/ejec_ing_Dep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18b2bf002babd020/Documentos/boletin_des/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{1E27EB45-4F89-4BA1-8CD2-6D4B446A65EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5ED05E-27B4-49B8-BF42-CCA4C7F4BFFF}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{1E27EB45-4F89-4BA1-8CD2-6D4B446A65EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B94B379A-841A-44AA-A514-CEED50292C5D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{51870C50-6AD8-43F7-B15A-A83F4E3AB875}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{51870C50-6AD8-43F7-B15A-A83F4E3AB875}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="4" r:id="rId1"/>
@@ -791,13 +791,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E95111-C17E-4C12-B211-2F8B1C44D3FA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F161"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -817,7 +818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>2021</v>
       </c>
@@ -837,7 +838,7 @@
         <v>15046740284884</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2021</v>
       </c>
@@ -857,7 +858,7 @@
         <v>5487097943572</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2021</v>
       </c>
@@ -877,7 +878,7 @@
         <v>1605455802337</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>2021</v>
       </c>
@@ -897,7 +898,7 @@
         <v>1624582239640</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>2021</v>
       </c>
@@ -917,7 +918,7 @@
         <v>1398161414300</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>2021</v>
       </c>
@@ -937,7 +938,7 @@
         <v>970423687672</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>2021</v>
       </c>
@@ -957,7 +958,7 @@
         <v>429853016359</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>2021</v>
       </c>
@@ -977,7 +978,7 @@
         <v>1629618516217</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>2021</v>
       </c>
@@ -997,7 +998,7 @@
         <v>974211877613</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>2021</v>
       </c>
@@ -1017,7 +1018,7 @@
         <v>1485045608722</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>2021</v>
       </c>
@@ -1037,7 +1038,7 @@
         <v>3540555935364</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>2021</v>
       </c>
@@ -1057,7 +1058,7 @@
         <v>647536462265</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>2021</v>
       </c>
@@ -1077,7 +1078,7 @@
         <v>1028803453711</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>2021</v>
       </c>
@@ -1097,7 +1098,7 @@
         <v>704008407004</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>2021</v>
       </c>
@@ -1117,7 +1118,7 @@
         <v>1299671233582</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>2021</v>
       </c>
@@ -1137,7 +1138,7 @@
         <v>987464488130</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>2021</v>
       </c>
@@ -1157,7 +1158,7 @@
         <v>1420884945493</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>2021</v>
       </c>
@@ -1177,7 +1178,7 @@
         <v>1109695297180</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>2021</v>
       </c>
@@ -1197,7 +1198,7 @@
         <v>448222431964</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>2021</v>
       </c>
@@ -1217,7 +1218,7 @@
         <v>670380377776</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>2021</v>
       </c>
@@ -1237,7 +1238,7 @@
         <v>1817063664840</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>2021</v>
       </c>
@@ -1257,7 +1258,7 @@
         <v>886803215789</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>2021</v>
       </c>
@@ -1277,7 +1278,7 @@
         <v>1361590063040</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>2021</v>
       </c>
@@ -1297,7 +1298,7 @@
         <v>3008588823343</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>2021</v>
       </c>
@@ -1317,7 +1318,7 @@
         <v>447720037748</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>2021</v>
       </c>
@@ -1337,7 +1338,7 @@
         <v>491323790118</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>2021</v>
       </c>
@@ -1357,7 +1358,7 @@
         <v>264414223813</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>2021</v>
       </c>
@@ -1377,7 +1378,7 @@
         <v>238762457205</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>2021</v>
       </c>
@@ -1397,7 +1398,7 @@
         <v>256861715071</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>2021</v>
       </c>
@@ -1417,7 +1418,7 @@
         <v>239268457081</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>2021</v>
       </c>
@@ -1437,7 +1438,7 @@
         <v>190722044256</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>2021</v>
       </c>
@@ -1457,7 +1458,7 @@
         <v>178472860837</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>2022</v>
       </c>
@@ -1477,7 +1478,7 @@
         <v>23816385889236</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>2022</v>
       </c>
@@ -1497,7 +1498,7 @@
         <v>6094580316867</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>2022</v>
       </c>
@@ -1517,7 +1518,7 @@
         <v>1945881555259</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>2022</v>
       </c>
@@ -1537,7 +1538,7 @@
         <v>1842629931053</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>2022</v>
       </c>
@@ -1557,7 +1558,7 @@
         <v>1558497524803</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>2022</v>
       </c>
@@ -1577,7 +1578,7 @@
         <v>1020938968677</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>2022</v>
       </c>
@@ -1597,7 +1598,7 @@
         <v>459959031950</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>2022</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>1692022472551</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>2022</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>1081044554832</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>2022</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>1688056645777</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>2022</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>4436215832804</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>2022</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>652769335172</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>2022</v>
       </c>
@@ -1717,7 +1718,7 @@
         <v>1171897419517</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>2022</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>670157333978</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>2022</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>1512396988840</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>2022</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>1054437914098</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>2022</v>
       </c>
@@ -1797,7 +1798,7 @@
         <v>1531099081512</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>2022</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>1466013259563</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>2022</v>
       </c>
@@ -1837,7 +1838,7 @@
         <v>515427264353</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>2022</v>
       </c>
@@ -1857,7 +1858,7 @@
         <v>976093341196</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>2022</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>2132164016925</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>2022</v>
       </c>
@@ -1897,7 +1898,7 @@
         <v>994996367353</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>2022</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>1432330825143</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>2022</v>
       </c>
@@ -1937,7 +1938,7 @@
         <v>3294744325609</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>2022</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>388415285223</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>2022</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>551518900693</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>2022</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>553766543446</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>2022</v>
       </c>
@@ -2017,7 +2018,7 @@
         <v>299644425561</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>2022</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>252661890722</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>2022</v>
       </c>
@@ -2057,7 +2058,7 @@
         <v>235078028945</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>2022</v>
       </c>
@@ -2077,7 +2078,7 @@
         <v>226360368227</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>2022</v>
       </c>
@@ -2097,7 +2098,7 @@
         <v>197072728489</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>2023</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>26438064291230</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>2023</v>
       </c>
@@ -2137,7 +2138,7 @@
         <v>7058839859780</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>96</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v>2268232844727</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>96</v>
       </c>
@@ -2177,7 +2178,7 @@
         <v>1884941445046</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>96</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>1674641654546</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>96</v>
       </c>
@@ -2217,7 +2218,7 @@
         <v>1167464460959</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>96</v>
       </c>
@@ -2237,7 +2238,7 @@
         <v>484647697585</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>96</v>
       </c>
@@ -2257,7 +2258,7 @@
         <v>1884143537944</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>96</v>
       </c>
@@ -2277,7 +2278,7 @@
         <v>1221376108502</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>96</v>
       </c>
@@ -2297,7 +2298,7 @@
         <v>1769753699940</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>96</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>4831295205438</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>96</v>
       </c>
@@ -2337,7 +2338,7 @@
         <v>716169744177</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>96</v>
       </c>
@@ -2357,7 +2358,7 @@
         <v>1264051341503</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>96</v>
       </c>
@@ -2377,7 +2378,7 @@
         <v>792779337182</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>96</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>1826174021668</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>96</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>1227911772376</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>96</v>
       </c>
@@ -2437,7 +2438,7 @@
         <v>1725148638412</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>2023</v>
       </c>
@@ -2457,7 +2458,7 @@
         <v>1604272644208</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>96</v>
       </c>
@@ -2477,7 +2478,7 @@
         <v>587929617299</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>96</v>
       </c>
@@ -2497,7 +2498,7 @@
         <v>1106956286123</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>96</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>2303962284612</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>96</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>1052515037706</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>96</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>1514888686744</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>96</v>
       </c>
@@ -2577,7 +2578,7 @@
         <v>3867353625662</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>96</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>426731038728</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>96</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>621613941567</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>96</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>603741931760</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>96</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>309634686019</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>96</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>286849396036</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>96</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>260650373517</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>96</v>
       </c>
@@ -2717,7 +2718,7 @@
         <v>242755653468</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>96</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v>229312395059</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>2024</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>30298178001994</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>2024</v>
       </c>
@@ -2777,7 +2778,7 @@
         <v>7768858805216</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>2024</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>2095191053782</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>2024</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>2017017615862</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>2024</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>1960007734567</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>2024</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>1291232593965</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>2024</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>557278011978</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>2024</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>2136668083797</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>2024</v>
       </c>
@@ -2917,7 +2918,7 @@
         <v>1459249800484</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>2024</v>
       </c>
@@ -2937,7 +2938,7 @@
         <v>1981459875841</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>2024</v>
       </c>
@@ -2957,7 +2958,7 @@
         <v>4753412336599</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>2024</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>941266470122</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>2024</v>
       </c>
@@ -2997,7 +2998,7 @@
         <v>1350470711818</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>2024</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>885845604958</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>2024</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>2093824467986</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>2024</v>
       </c>
@@ -3057,7 +3058,7 @@
         <v>1399659343677</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>2024</v>
       </c>
@@ -3077,7 +3078,7 @@
         <v>1978412986051</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>2024</v>
       </c>
@@ -3097,7 +3098,7 @@
         <v>1715666094998</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>2024</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>667195859647</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>2024</v>
       </c>
@@ -3137,7 +3138,7 @@
         <v>1081362965764</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>2024</v>
       </c>
@@ -3157,7 +3158,7 @@
         <v>2511062106004</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>2024</v>
       </c>
@@ -3177,7 +3178,7 @@
         <v>1213938951665</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>2024</v>
       </c>
@@ -3197,7 +3198,7 @@
         <v>1635924854862</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>2024</v>
       </c>
@@ -3217,7 +3218,7 @@
         <v>3705635596055</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>2024</v>
       </c>
@@ -3237,7 +3238,7 @@
         <v>518417715484</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>2024</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>738329279455</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>2024</v>
       </c>
@@ -3277,7 +3278,7 @@
         <v>712425151118</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>2024</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>490103008745</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>2024</v>
       </c>
@@ -3317,7 +3318,7 @@
         <v>355943194515</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>2024</v>
       </c>
@@ -3337,7 +3338,7 @@
         <v>290997518430</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>2024</v>
       </c>
@@ -3357,7 +3358,7 @@
         <v>314214287860</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>2024</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>343437820063</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>35</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>32814933177692</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>35</v>
       </c>
@@ -3417,7 +3418,7 @@
         <v>8440529658756</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>35</v>
       </c>
@@ -3437,7 +3438,7 @@
         <v>2482567485022</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>35</v>
       </c>
@@ -3457,7 +3458,7 @@
         <v>2450352249875</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>35</v>
       </c>
@@ -3477,7 +3478,7 @@
         <v>2220456789711</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>35</v>
       </c>
@@ -3497,7 +3498,7 @@
         <v>1431210623555</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>35</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>776562103047</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>35</v>
       </c>
@@ -3537,7 +3538,7 @@
         <v>2591551602597</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>35</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>1636183717009</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>35</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>2326655904280</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>35</v>
       </c>
@@ -3597,7 +3598,7 @@
         <v>6307630890327</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>35</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>1118182741204</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>35</v>
       </c>
@@ -3637,7 +3638,7 @@
         <v>1635628196066</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>35</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>1091930743254</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>35</v>
       </c>
@@ -3677,7 +3678,7 @@
         <v>2082340500804</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>35</v>
       </c>
@@ -3697,7 +3698,7 @@
         <v>1592227326989</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>35</v>
       </c>
@@ -3717,7 +3718,7 @@
         <v>2415433823402</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>35</v>
       </c>
@@ -3737,7 +3738,7 @@
         <v>2061808214666</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>35</v>
       </c>
@@ -3757,7 +3758,7 @@
         <v>663333805982</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>35</v>
       </c>
@@ -3777,7 +3778,7 @@
         <v>1329703361772</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>35</v>
       </c>
@@ -3797,7 +3798,7 @@
         <v>2835778701314</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>35</v>
       </c>
@@ -3817,7 +3818,7 @@
         <v>1367556294068</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>35</v>
       </c>
@@ -3837,7 +3838,7 @@
         <v>1986546181451</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>35</v>
       </c>
@@ -3857,7 +3858,7 @@
         <v>4204844198476</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>35</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v>615297095767</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>35</v>
       </c>
@@ -3897,7 +3898,7 @@
         <v>1063960716134</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>35</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>874149929061</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>35</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>507162677805</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>35</v>
       </c>
@@ -3957,7 +3958,7 @@
         <v>420103107283</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>35</v>
       </c>
@@ -3977,7 +3978,7 @@
         <v>365729958936</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>35</v>
       </c>
@@ -3997,7 +3998,7 @@
         <v>366172414404</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>35</v>
       </c>
@@ -4018,7 +4019,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F161" xr:uid="{F3E95111-C17E-4C12-B211-2F8B1C44D3FA}"/>
+  <autoFilter ref="A1:F161" xr:uid="{F3E95111-C17E-4C12-B211-2F8B1C44D3FA}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Bogotá,D.C."/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>